--- a/AAII_Financials/Quarterly/DIS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DIS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>DIS</t>
   </si>
@@ -656,522 +656,534 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44107</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25248000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25168000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25981000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22464000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23650000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23621000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24690000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22574000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23155000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22083000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23549000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21241000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22330000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21815000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23512000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20150000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21504000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19249000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>21819000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18534000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17022000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15613000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16249000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14707000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11779000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18025000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20877000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>19137000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20245000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14922000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15303000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14307000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15228000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>14548000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>15351000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>12779000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>14238000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>13336000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>14784000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13142000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15106000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15901000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16669000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14018000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14532000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14810000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15406000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14230000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14709000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14172000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15587000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13728000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14471000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14616000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16386000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13558000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13682000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12594000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14567000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12341000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11233000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9782000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11775000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11013000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7896000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11937000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13034000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11865000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12819000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8376000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>9001000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8108000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8348000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7533000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8737000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7214000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7717000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6969000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>8406000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>7305000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10142000</v>
+      </c>
+      <c r="E10" s="3">
         <v>9267000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9312000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8446000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9118000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8811000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9284000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8344000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8446000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7911000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7962000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7513000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7859000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7199000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>7126000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6592000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7822000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6655000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7252000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6193000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5789000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5831000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4474000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3694000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3883000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6088000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7843000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7272000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7426000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>6546000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>6302000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6199000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6880000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7015000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6614000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5565000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6521000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6367000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6378000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5837000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1214,8 +1226,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1336,8 +1349,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,119 +1474,122 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>900000</v>
+      </c>
+      <c r="E14" s="3">
         <v>239000</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>382000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>185000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>109000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>143000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1543000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2052000</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1049000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2560000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>69000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>42000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>195000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>92000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-91000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>414000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>113000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>393000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5047000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>440000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>150000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>825000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>515000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-3948000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>5000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>13000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>98000</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
@@ -1578,132 +1597,138 @@
         <v>0</v>
       </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1405000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1316000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1394000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1332000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1324000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1276000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1285000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1220000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1242000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1243000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1409000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1344000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1310000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1306000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1317000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1290000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1287000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1269000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1275000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1266000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1272000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1298000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1335000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1377000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1334000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1299000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1303000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1304000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>828000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>732000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>794000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>744000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>731000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>742000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>708000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>711000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>676000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>687000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>689000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1743,252 +1768,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20375000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21264000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21990000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19798000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19938000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20050000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20546000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19727000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19702000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19101000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20513000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19075000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19602000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19456000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21560000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>19608000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19114000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17844000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19627000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17927000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15576000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14581000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16103000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15553000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>16775000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16809000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18192000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17698000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>18000000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7583000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11885000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11229000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11304000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10524000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11573000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9993000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10627000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>9586000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>11078000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>10312000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4873000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3904000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3991000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2666000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3712000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3571000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4144000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2847000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3453000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2982000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3036000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2166000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2728000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2359000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1952000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>542000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2390000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1405000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2192000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>607000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1446000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>146000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-846000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4996000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1216000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2685000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1439000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2245000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7339000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3418000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3078000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3924000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4024000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3778000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2786000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3611000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3750000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3706000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2830000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2031,618 +2063,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-57000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-93000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-92000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-75000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-36000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-92000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-107000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-81000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-141000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-181000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-250000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-90000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>286000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>268000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-143000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-47000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>613000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>304000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>730000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>623000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>908000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>653000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>613000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>230000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>78000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>162000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>313000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>105000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>76000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>113000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>45000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>141000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>116000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>140000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>170000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6370000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5366000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5400000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4152000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5119000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4931000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5512000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4239000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4754000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4365000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4460000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3825000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4162000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3842000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3544000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2127000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3789000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2763000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3318000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1888000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2665000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2917000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1748000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1219000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2994000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3457000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4636000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3348000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3779000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8245000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4312000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4185000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4773000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4831000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4633000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3539000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4463000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>4542000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>4533000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3689000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E22" s="3">
         <v>473000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>443000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>416000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>438000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>471000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>487000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>532000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>509000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>501000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>528000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>501000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>503000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>504000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>465000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>434000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>380000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>374000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>361000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>323000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>404000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>415000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>404000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>464000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>467000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1073000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>712000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>815000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>457000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>180000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>149000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>189000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>172000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>146000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>137000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>134000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>115000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>121000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>119000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3645000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3367000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3693000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2045000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3211000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3087000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3660000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>948000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3093000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>657000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2871000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1007000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-134000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2123000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1773000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>376000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2119000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1102000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1688000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>290000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>995000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1230000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>46000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-580000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4840000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1051000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2626000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1237000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2018000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7237000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3431000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3202000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3854000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3928000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3745000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2694000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3618000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3725000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2881000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>801000</v>
+      </c>
+      <c r="E24" s="3">
         <v>902000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1209000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>602000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2732000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-314000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1016000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>384000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>251000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>441000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>720000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>313000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>635000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>412000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>122000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>617000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>505000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>488000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>34000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-133000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>49000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-331000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>523000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>458000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>339000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>395000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1647000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>679000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>683000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>895000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>913000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>872000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>829000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1144000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1212000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1237000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>989000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2763,252 +2811,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2844000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2465000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2484000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1443000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5943000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3401000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2644000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>564000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2842000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>216000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2151000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>694000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-153000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1488000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1361000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>254000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1502000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>597000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>256000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1128000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1122000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-629000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4509000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>528000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2168000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>898000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1623000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5590000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2752000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2519000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2959000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3015000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2873000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1865000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2474000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2539000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2488000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1892000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2638000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2247000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2402000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1313000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5262000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3275000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2554000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>460000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2621000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1911000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>264000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-460000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1279000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>162000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1409000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>470000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1152000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>160000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>923000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>912000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4718000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>468000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2128000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>769000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1437000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5431000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2754000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2422000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2816000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2837000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2823000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1747000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2366000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2388000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1771000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3129,8 +3186,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3186,58 +3246,58 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-48000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-5000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>285000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>323000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>21000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>34000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-100000</v>
-      </c>
-      <c r="AI29" s="3">
-        <v>100000</v>
       </c>
       <c r="AJ29" s="3">
         <v>100000</v>
       </c>
       <c r="AK29" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1600000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3251,8 +3311,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3373,8 +3436,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3495,252 +3561,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E32" s="3">
         <v>57000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>93000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>92000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>75000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>36000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>92000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>107000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>81000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>141000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>181000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>250000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>90000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>173000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-286000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-268000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>143000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>47000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-613000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-304000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-730000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-623000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-908000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-653000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-613000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-230000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-78000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-313000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-105000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-113000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-45000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-116000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-140000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2638000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2247000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2402000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1313000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5262000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3275000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2554000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>460000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2621000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1911000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>264000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-460000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1279000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>162000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1409000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>470000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1104000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>159000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>918000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>901000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4721000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>460000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2107000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1760000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5452000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2788000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2322000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2916000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2937000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4423000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1747000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2366000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2388000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2479000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1771000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3861,257 +3936,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2638000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2247000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2402000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1313000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5262000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3275000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2554000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>460000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2621000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1911000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>264000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-460000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1279000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>162000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1409000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>470000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1104000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>159000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>918000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>901000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4721000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>460000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2107000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1760000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5452000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2788000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2322000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2916000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2937000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4423000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1747000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2366000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2388000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2479000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1771000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44107</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4154,8 +4238,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4198,130 +4283,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5185000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5682000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5678000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5695000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5367000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5852000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5486000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6002000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5954000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6635000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7192000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14182000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11458000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10399000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8470000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11615000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12959000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13272000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14444000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15959000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16070000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15890000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17068000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>17914000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>23115000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14339000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6833000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5418000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6728000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10208000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4455000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4150000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4326000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4179000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4677000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4017000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4336000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3800000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3736000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>4610000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4442,862 +4531,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14553000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14390000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15054000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13217000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13402000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12571000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13767000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12729000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12966000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12026000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14115000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12330000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13112000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12770000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13993000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12652000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13685000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13746000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14882000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13367000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13355000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12533000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14051000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12708000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12622000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14532000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17100000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15481000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15673000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14593000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>10123000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9334000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10071000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9678000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9886000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8633000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9636000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9293000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>9878000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9065000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4015000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3247000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3493000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4197000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3836000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3062000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3175000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4119000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3976000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3869000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3363000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4965000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4269000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3720000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1830000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1742000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1590000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1428000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1345000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1331000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1344000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1406000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1480000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1583000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1559000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1531000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1571000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1649000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1516000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1445000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1357000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1392000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1322000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1301000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1307000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1373000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1300000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1304000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1299000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1390000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1280000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1241000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1158000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1207000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1243000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1239000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2391000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2597000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2106000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1301000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1286000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1332000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1371000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2619000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3089000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3188000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2981000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2242000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3000000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3197000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3048000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2275000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3046000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4034000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2872000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2272000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5576000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7453000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8031000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1602000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1949000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2010000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1650000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1404000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1866000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1879000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1873000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1752000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1901000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24892000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24599000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25466000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24267000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23820000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22735000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23667000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25241000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25493000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24636000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25971000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32763000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30174000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>28263000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26912000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29098000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31422000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31427000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32913000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>33657000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>33966000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>32877000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>34874000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>35251000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41330000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>33274000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27776000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>28124000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>31370000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>34277000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17537000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16825000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17729000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16808000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17274000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15889000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17151000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>16270000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>16665000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>16966000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7627000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8397000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8052000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8097000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8671000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8794000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8902000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4459000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4632000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3007000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3084000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3080000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3062000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3387000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3169000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3218000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3236000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3356000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3549000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3935000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4045000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4309000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4037000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3903000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3611000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3180000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3312000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3224000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3872000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4080000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2970000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2899000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3155000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3148000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3206000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3202000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4141000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4187000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>4259000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>4280000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44744000</v>
+      </c>
+      <c r="E48" s="3">
         <v>44255000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43198000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44646000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40185000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39095000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38140000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>40663000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36041000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35525000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35321000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39443000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34577000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34579000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34200000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37865000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33583000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>32917000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>32681000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36855000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32377000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32137000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32263000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>36126000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>36137000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>36715000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35503000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31603000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31392000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31017000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>29797000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>29540000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>29373000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>29200000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>28584000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>28406000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>27733000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>27399000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>27054000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>27349000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>84468000</v>
+      </c>
+      <c r="E49" s="3">
         <v>84744000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>84172000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>82566000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>82953000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>83319000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>83684000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84065000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>85021000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>85388000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>89705000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>90128000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>91359000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>91765000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>128480000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>128511000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>127356000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>126243000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>125295000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>124735000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>123325000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>122842000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>122371000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>121884000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>122382000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>129114000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>129522000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>126318000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>125467000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>126395000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>46213000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>45969000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>45882000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>46386000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>46297000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>45902000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>41430000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>41650000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>41257000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>41098000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5418,8 +5531,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5540,130 +5656,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41928000</v>
+      </c>
+      <c r="E52" s="3">
         <v>43222000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>41201000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36662000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39983000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40890000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41653000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40491000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>46185000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45454000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42493000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38865000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44111000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>45764000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9363000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4939000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8477000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8510000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8873000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4427000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8508000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8085000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8343000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4385000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4189000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4011000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4835000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4715000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17374000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>18573000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3424000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3365000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2653000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2401000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2373000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2390000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2297000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2301000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2341000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2340000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5784,130 +5906,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>204740000</v>
+      </c>
+      <c r="E54" s="3">
         <v>205217000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>202089000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>197514000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>196612000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>195833000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>197046000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>196219000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>197772000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>195110000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>197774000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>205579000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>203783000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>204858000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>202124000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>203631000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>204074000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>202453000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>203311000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>203609000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>202221000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>200250000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>201888000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>201549000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>207649000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>206294000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>200948000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>193984000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>209475000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>214342000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>99941000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>98598000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>98792000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>97943000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>97734000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>95789000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>92752000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>91807000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>91576000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>92033000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5950,8 +6078,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5994,740 +6123,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19548000</v>
+      </c>
+      <c r="E57" s="3">
         <v>19961000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20541000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14509000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20500000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20729000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21635000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14022000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20216000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18798000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18676000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14348000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19115000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18591000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18149000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20213000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20858000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19669000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18709000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20894000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18317000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17062000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>16846000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16017000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16144000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>17048000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>18920000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>17762000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>17647000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>20503000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10696000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9479000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9763000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9022000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9574000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6490000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8987000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>7678000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>9616000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>6860000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8627000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8887000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10819000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7257000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5732000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6446000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6620000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7619000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8060000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6789000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6087000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5107000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2645000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3452000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3249000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3070000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5580000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5399000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6783000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5866000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4728000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5243000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5397000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5748000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10262000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12712000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10047000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8857000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>21923000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19158000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3489000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3790000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5992000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5918000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6009000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6172000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3338000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4865000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5698000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3687000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6930000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7375000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6686000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8809000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6740000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6854000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6591000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9286000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7336000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7287000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6270000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8623000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6474000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6013000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5672000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5790000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4266000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4533000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4545000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4317000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4368000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4337000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4303000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4863000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4511000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5713000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5830000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4722000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5023000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4715000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3434000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4591000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4459000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4788000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4292000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6933000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4769000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4822000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4003000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>6295000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35105000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36223000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38046000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34162000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32972000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34029000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34846000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34599000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35612000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32874000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31033000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31139000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28234000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28056000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27070000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29073000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>30704000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29601000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30037000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31077000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27413000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26642000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26546000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>26628000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30917000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>35473000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>34797000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>31341000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>44593000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>44376000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17619000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>17860000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>20214000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19728000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>19875000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>19595000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>17094000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>17365000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>19317000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>16842000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37414000</v>
+      </c>
+      <c r="E61" s="3">
         <v>38471000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35821000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38166000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36531000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36443000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>38688000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41898000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39524000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39510000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41603000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45565000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44544000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45066000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45128000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>45299000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46022000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46624000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>47349000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>48540000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>51110000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>50903000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>52878000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>53188000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>54468000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>43052000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>38309000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>38129000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36311000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37803000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>17176000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>17084000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17681000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18766000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>20082000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19119000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>18849000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>16788000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>14792000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>16483000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9467000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9438000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9357000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6265000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9438000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9431000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9553000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7065000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9817000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11193000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11644000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7628000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11925000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12362000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21048000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20881000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21490000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22215000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22332000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21768000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23084000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>23509000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24406000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24221000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>22639000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>23796000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24040000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21662000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>23318000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>26721000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9629000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9699000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9689000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9648000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9552000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>10923000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>10758000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>10387000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>10290000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>11385000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6848,8 +6996,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6970,8 +7121,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7092,130 +7246,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87898000</v>
+      </c>
+      <c r="E66" s="3">
         <v>89905000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88081000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>82902000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82856000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87067000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90307000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>90697000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>92469000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91347000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>92273000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>92567000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>92841000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94488000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105975000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>108623000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>111574000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>111817000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>113447000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>115056000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>115480000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>114710000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>117817000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>117966000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>121783000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>115887000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>111191000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>105107000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>119003000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>124404000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49625000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>49825000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>52704000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>52792000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>54445000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>54474000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>50221000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>48023000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>48366000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>48768000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7258,8 +7418,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7380,8 +7541,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7502,8 +7666,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7624,8 +7791,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7746,130 +7916,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65052000</v>
+      </c>
+      <c r="E72" s="3">
         <v>62393000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>60164000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>60410000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>59109000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53733000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50468000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49722000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49273000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46649000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47490000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>46093000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>45794000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46236000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>44955000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>43636000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>43462000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42032000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>41547000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>40429000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>40311000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>39365000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>38456000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>38315000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39004000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>43721000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>43202000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>42494000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>41382000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>41212000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>84887000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>82679000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>80364000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>78704000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>75763000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>72606000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>70863000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>69708000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>67327000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>66088000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7990,8 +8166,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8112,8 +8291,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8234,130 +8416,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110032000</v>
+      </c>
+      <c r="E76" s="3">
         <v>108708000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>108476000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>109869000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>109145000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>104339000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101933000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>100696000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>100622000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>99252000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>100721000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>99277000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97610000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97859000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>96149000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>95008000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>92500000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>90636000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>89864000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>88553000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>86741000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>85540000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>84071000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>83583000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>85866000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>90407000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>89757000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>88877000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>90472000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>89938000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>50316000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>48773000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>46088000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>45151000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>43289000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>41315000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>42531000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>43784000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>43210000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>43265000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8478,257 +8666,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44107</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2638000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2247000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2402000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1313000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5262000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3275000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2554000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>460000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2621000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1911000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>264000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-460000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1279000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>162000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1409000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>470000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1104000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>159000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>918000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>901000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-710000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4721000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>460000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2107000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1760000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5452000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2788000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2322000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2916000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2937000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4423000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1747000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2366000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2388000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2479000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1771000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8771,130 +8968,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E83" s="3">
         <v>957000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>909000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>918000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>854000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>839000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>823000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1007000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>946000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>845000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>828000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>825000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>805000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>786000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1306000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1317000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1290000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1287000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1269000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1275000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1266000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1272000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1298000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1335000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1379000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1333000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1298000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1296000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1304000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>828000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>732000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>794000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>744000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>731000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>742000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>708000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>711000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>676000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>687000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>689000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9015,8 +9216,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9137,8 +9341,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9259,8 +9466,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9381,8 +9591,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9503,130 +9716,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4866000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6914000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>735000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4474000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3669000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6753000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3205000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5518000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2602000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3666000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2185000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4802000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2802000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3236000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-974000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2524000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1922000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1765000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-201000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2635000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1460000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>84000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1667000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1160000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3180000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1611000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2020000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1393000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3880000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2099000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3853000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3679000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4526000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2237000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3512000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>4133000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3253000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1445000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3598000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9669,130 +9888,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1794000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1973000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3013000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1916000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1780000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1862000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2466000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1489000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1365000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1259000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1299000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1374000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1165000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1249000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1148000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1735000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-981000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1110000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-938000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-770000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-760000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-729000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-708000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1247000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1338000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1177000</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-1195000</v>
       </c>
       <c r="AG91" s="3">
         <v>-1195000</v>
       </c>
       <c r="AH91" s="3">
+        <v>-1195000</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-1201000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1220000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1063000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-981000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-895000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-805000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1766000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2080000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-2164000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9913,8 +10136,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10035,130 +10261,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1787000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2732000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2737000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1850000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1720000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1898000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2575000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1978000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2350000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1307000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1246000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1382000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-718000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1249000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1292000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1136000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1848000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-987000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1086000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-754000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-591000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-732000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-515000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-714000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1058000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1350000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>9667000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1102000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11347000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1336000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-193000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1338000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2762000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1043000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-821000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-900000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1355000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1532000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10201,40 +10433,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1337000</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>898000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>905000</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>817000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>549000</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
@@ -10245,8 +10478,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10285,11 +10518,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1585000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10297,11 +10530,11 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1249000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10309,11 +10542,11 @@
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-1208000</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
@@ -10321,10 +10554,13 @@
         <v>0</v>
       </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-1145000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10445,8 +10681,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10567,8 +10806,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10689,370 +10931,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3578000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4146000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1984000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2276000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2537000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4556000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-997000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3566000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-898000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2818000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8006000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-597000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1001000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1043000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2482000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-150000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1817000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-292000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1614000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-530000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1908000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-333000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6439000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8303000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5499000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1117000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13444000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-342000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>13107000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-411000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3862000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2099000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2298000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-584000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3167000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2743000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2062000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-987000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2900000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E101" s="3">
         <v>77000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-153000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>79000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-31000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-62000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>79000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-101000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>164000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-249000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-238000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>164000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-249000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-238000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-81000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-35000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-47000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>139000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>87000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>27000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>41000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-145000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>119000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>26000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-106000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>34000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>21000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>54000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>46000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>43000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-112000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-490000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>322000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-481000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>376000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-520000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-677000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-521000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6988000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2722000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1060000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1937000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3145000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1343000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-314000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1170000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1515000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-112000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>183000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1180000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-842000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5200000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8776000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7504000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1419000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1902000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2865000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5759000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>308000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-176000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>136000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-500000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>631000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>536000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-121000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-689000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-617000</v>
       </c>
     </row>
